--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4833.65</v>
+        <v>4902.82</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20653.53</v>
+        <v>20949.06</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>736.1799999999999</v>
+        <v>746.72</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>622.72</v>
+        <v>631.63</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>674.78</v>
+        <v>684.4299999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7956.29</v>
+        <v>8070.14</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>702.66</v>
+        <v>712.71</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>591.5599999999999</v>
+        <v>600.03</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8564.49</v>
+        <v>8687.040000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>584.98</v>
+        <v>593.35</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>858.53</v>
+        <v>870.8099999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8564.49</v>
+        <v>8687.040000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3640.7</v>
+        <v>3692.8</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>954.75</v>
+        <v>968.41</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7888.44</v>
+        <v>8001.32</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>503.59</v>
+        <v>510.8</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1022.26</v>
+        <v>1036.88</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4419.04</v>
+        <v>4482.27</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8365.49</v>
+        <v>8485.200000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>736.1799999999999</v>
+        <v>746.72</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7888.44</v>
+        <v>8001.32</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4086.14</v>
+        <v>4144.6</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8516.120000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8365.57</v>
+        <v>8463.700000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1354.42</v>
+        <v>1370.31</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8365.57</v>
+        <v>8463.700000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1228.06</v>
+        <v>1242.47</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8365.57</v>
+        <v>8463.700000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>655.37</v>
+        <v>663.0599999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>21136.99</v>
+        <v>21384.94</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1584.67</v>
+        <v>1603.26</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8618.26</v>
+        <v>8719.35</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>693.2</v>
+        <v>701.33</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>495.52</v>
+        <v>501.34</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>965.13</v>
+        <v>976.45</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1116.59</v>
+        <v>1129.69</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7968.05</v>
+        <v>8061.52</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8361.75</v>
+        <v>8459.84</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>322.47</v>
+        <v>326.25</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>763.8200000000001</v>
+        <v>772.78</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11446.3</v>
+        <v>11580.57</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3196.47</v>
+        <v>3233.97</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>493.35</v>
+        <v>499.14</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>413.05</v>
+        <v>420.04</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2076.6</v>
+        <v>2111.72</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>700.04</v>
+        <v>711.88</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>15912.58</v>
+        <v>16181.7</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1005.38</v>
+        <v>1022.38</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>997.8</v>
+        <v>1014.68</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>990.63</v>
+        <v>1007.38</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>677.26</v>
+        <v>688.71</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2006.26</v>
+        <v>2040.19</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1494.69</v>
+        <v>1519.97</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8365.57</v>
+        <v>8507.049999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8361.75</v>
+        <v>8503.17</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>644.51</v>
+        <v>655.41</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5097.22</v>
+        <v>5183.43</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8618.26</v>
+        <v>8764.01</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>633.8200000000001</v>
+        <v>644.54</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7968.05</v>
+        <v>8102.81</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1368.74</v>
+        <v>1391.89</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7785.52</v>
+        <v>7917.19</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8559.73</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6533.36</v>
+        <v>6643.85</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>411.48</v>
+        <v>418.44</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8361.75</v>
+        <v>8503.17</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8618.26</v>
+        <v>8764.01</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9286.75</v>
+        <v>9381.190000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11053.99</v>
+        <v>11166.4</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>13432.19</v>
+        <v>13568.79</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>169.09</v>
+        <v>170.68</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>520.1900000000001</v>
+        <v>525.0700000000001</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1362.85</v>
+        <v>1375.63</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8496.32</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>676.02</v>
+        <v>682.36</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2645.96</v>
+        <v>2670.78</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8496.32</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>511.13</v>
+        <v>515.92</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>9862.629999999999</v>
+        <v>9955.129999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>510.09</v>
+        <v>514.88</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>172.54</v>
+        <v>174.16</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12458.17</v>
+        <v>12575.02</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8361.75</v>
+        <v>8440.18</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8496.32</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1070.71</v>
+        <v>1080.75</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>699.34</v>
+        <v>705.9</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8618.26</v>
+        <v>8699.09</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>9074.209999999999</v>
+        <v>9159.32</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8564.49</v>
+        <v>8644.82</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>772.4299999999999</v>
+        <v>779.67</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>17689</v>
+        <v>17854.91</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>277.57</v>
+        <v>280.18</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1427.61</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>19322.62</v>
+        <v>19503.85</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8618.26</v>
+        <v>8699.09</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>8361.75</v>
+        <v>8440.18</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>511.13</v>
+        <v>515.92</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>7956.29</v>
+        <v>8030.91</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>200.82</v>
+        <v>202.7</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>16834.75</v>
+        <v>16992.65</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2564.12</v>
+        <v>2588.17</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8496.32</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>937.4299999999999</v>
+        <v>946.23</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2094.01</v>
+        <v>2078.12</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6145.32</v>
+        <v>6098.7</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>769402.91</v>
+        <v>763566.01</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3115.08</v>
+        <v>3091.45</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>714.09</v>
+        <v>708.67</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3020.76</v>
+        <v>2997.84</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3862.69</v>
+        <v>3797.43</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5286</v>
+        <v>5196.69</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6524.83</v>
+        <v>6414.59</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>13824.84</v>
+        <v>13591.26</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7736.05</v>
+        <v>7605.35</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8875.76</v>
+        <v>8725.790000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1443.24</v>
+        <v>1418.86</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4833.78</v>
+        <v>4752.11</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>8365.49</v>
+        <v>8246.77</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>638.28</v>
+        <v>629.22</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>18143.42</v>
+        <v>17885.93</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8365.49</v>
+        <v>8246.77</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3099.4</v>
+        <v>3055.41</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3275.34</v>
+        <v>3228.85</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>849.7</v>
+        <v>837.64</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>16867.33</v>
+        <v>16627.95</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>169.08</v>
+        <v>166.68</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>169.08</v>
+        <v>166.68</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>469.08</v>
+        <v>462.42</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>736.08</v>
+        <v>725.63</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>8564.49</v>
+        <v>8442.940000000001</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>597.29</v>
+        <v>588.8200000000001</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7888.44</v>
+        <v>7776.49</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>483.17</v>
+        <v>476.32</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8433.67</v>
+        <v>8313.969999999999</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>18832.77</v>
+        <v>18565.49</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>836.02</v>
+        <v>824.16</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>7888.44</v>
+        <v>7776.49</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>561.7</v>
+        <v>553.73</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>478.72</v>
+        <v>471.92</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1346.62</v>
+        <v>1327.51</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>4894.05</v>
+        <v>4824.59</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4950.82</v>
+        <v>4880.56</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>842.9299999999999</v>
+        <v>830.97</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>898.51</v>
+        <v>886.16</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>339.97</v>
+        <v>335.29</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8564.49</v>
+        <v>8446.809999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>512.08</v>
+        <v>505.04</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8365.57</v>
+        <v>8250.620000000001</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>447.11</v>
+        <v>440.97</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7888.44</v>
+        <v>7780.06</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>841.7</v>
+        <v>830.13</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>8761.98</v>
+        <v>8641.59</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>8805.709999999999</v>
+        <v>8684.719999999999</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>700.17</v>
+        <v>690.55</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8761.98</v>
+        <v>8641.59</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1090.11</v>
+        <v>1075.13</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>20393.89</v>
+        <v>20113.67</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7956.29</v>
+        <v>7846.97</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>331.07</v>
+        <v>326.52</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>8844.5</v>
+        <v>8722.98</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>385.74</v>
+        <v>380.44</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>26533.5</v>
+        <v>26168.93</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>416.35</v>
+        <v>410.63</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>658.6799999999999</v>
+        <v>649.63</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>8365.57</v>
+        <v>8250.620000000001</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>774.26</v>
+        <v>763.62</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>17689</v>
+        <v>17579.34</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>31743.96</v>
+        <v>31547.15</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>547.59</v>
+        <v>544.1900000000001</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>8564.49</v>
+        <v>8511.4</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>204.66</v>
+        <v>203.39</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>172.54</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1570.2</v>
+        <v>1560.46</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>277.57</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>833.6</v>
+        <v>828.4299999999999</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8365.190000000001</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>464.84</v>
+        <v>461.96</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7956.29</v>
+        <v>7906.96</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>38312.02</v>
+        <v>38074.49</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>24206.79</v>
+        <v>24056.71</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>355.66</v>
+        <v>353.45</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1557.54</v>
+        <v>1547.88</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>6041.52</v>
+        <v>6004.07</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3072.66</v>
+        <v>3053.61</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>577.41</v>
+        <v>573.83</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>7888.44</v>
+        <v>7839.54</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3496.26</v>
+        <v>3512.14</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1575.08</v>
+        <v>1582.23</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6029.27</v>
+        <v>6056.65</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>10625.62</v>
+        <v>10673.88</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2107.63</v>
+        <v>2117.2</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>15586.91</v>
+        <v>15657.7</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>42686.97</v>
+        <v>42880.84</v>
       </c>
     </row>
     <row r="195">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3228.87</v>
+        <v>3276.94</v>
       </c>
     </row>
     <row r="196">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>38972.72</v>
+        <v>39553.03</v>
       </c>
     </row>
     <row r="197">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>37440.71</v>
+        <v>37998.21</v>
       </c>
     </row>
     <row r="198">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8577.4</v>
       </c>
     </row>
     <row r="199">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>7956.29</v>
+        <v>8107.55</v>
       </c>
     </row>
     <row r="200">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1224.92</v>
+        <v>1248.21</v>
       </c>
     </row>
     <row r="201">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8365.49</v>
+        <v>8524.530000000001</v>
       </c>
     </row>
     <row r="202">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1065.55</v>
+        <v>1085.81</v>
       </c>
     </row>
     <row r="203">
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>8365.49</v>
+        <v>8524.530000000001</v>
       </c>
     </row>
     <row r="204">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>635.55</v>
+        <v>647.63</v>
       </c>
     </row>
     <row r="205">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1275.59</v>
+        <v>1299.84</v>
       </c>
     </row>
     <row r="206">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4612.71</v>
+        <v>4700.4</v>
       </c>
     </row>
     <row r="207">
@@ -13086,7 +13086,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>800.53</v>
+        <v>815.75</v>
       </c>
     </row>
     <row r="208">
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>9081.610000000001</v>
+        <v>9254.27</v>
       </c>
     </row>
     <row r="209">
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>868.25</v>
+        <v>884.76</v>
       </c>
     </row>
     <row r="210">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>9081.610000000001</v>
+        <v>9254.27</v>
       </c>
     </row>
     <row r="211">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>9081.610000000001</v>
+        <v>9254.27</v>
       </c>
     </row>
     <row r="212">
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1016.48</v>
+        <v>1035.81</v>
       </c>
     </row>
     <row r="213">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>8361.75</v>
+        <v>8520.719999999999</v>
       </c>
     </row>
     <row r="214">
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>7968.05</v>
+        <v>8147.75</v>
       </c>
     </row>
     <row r="215">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>172.54</v>
+        <v>176.43</v>
       </c>
     </row>
     <row r="216">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7934.05</v>
+        <v>8112.99</v>
       </c>
     </row>
     <row r="217">
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>172.54</v>
+        <v>176.43</v>
       </c>
     </row>
     <row r="218">
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>7956.29</v>
+        <v>8135.73</v>
       </c>
     </row>
     <row r="219">
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>333.35</v>
+        <v>340.87</v>
       </c>
     </row>
     <row r="220">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>167.2</v>
+        <v>170.98</v>
       </c>
     </row>
     <row r="221">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>8365.49</v>
+        <v>8554.16</v>
       </c>
     </row>
     <row r="222">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>563.3099999999999</v>
+        <v>576.01</v>
       </c>
     </row>
     <row r="223">
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>262.08</v>
+        <v>267.99</v>
       </c>
     </row>
     <row r="224">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>248.99</v>
+        <v>254.61</v>
       </c>
     </row>
     <row r="225">
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1109.5</v>
+        <v>1134.53</v>
       </c>
     </row>
     <row r="226">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>898.13</v>
+        <v>918.38</v>
       </c>
     </row>
     <row r="227">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>265.22</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="228">
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>13832.53</v>
+        <v>14144.49</v>
       </c>
     </row>
     <row r="229">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1278.28</v>
+        <v>1307.11</v>
       </c>
     </row>
     <row r="230">
@@ -14489,7 +14489,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>8844.5</v>
+        <v>9043.969999999999</v>
       </c>
     </row>
     <row r="231">
@@ -14550,7 +14550,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3172.91</v>
+        <v>3194.81</v>
       </c>
     </row>
     <row r="232">
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>154.01</v>
+        <v>155.07</v>
       </c>
     </row>
     <row r="233">
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>8361.75</v>
+        <v>8419.48</v>
       </c>
     </row>
     <row r="234">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>17689</v>
+        <v>17811.13</v>
       </c>
     </row>
     <row r="235">
@@ -14794,7 +14794,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>17689</v>
+        <v>17811.13</v>
       </c>
     </row>
     <row r="236">
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>277.57</v>
+        <v>279.49</v>
       </c>
     </row>
     <row r="237">
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>369.24</v>
+        <v>371.79</v>
       </c>
     </row>
     <row r="238">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2260.09</v>
+        <v>2275.7</v>
       </c>
     </row>
     <row r="239">
@@ -15038,7 +15038,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>7956.29</v>
+        <v>8011.22</v>
       </c>
     </row>
     <row r="240">
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8761.98</v>
+        <v>8822.469999999999</v>
       </c>
     </row>
     <row r="241">
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>8761.98</v>
+        <v>8822.469999999999</v>
       </c>
     </row>
     <row r="242">
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3097.45</v>
+        <v>3118.84</v>
       </c>
     </row>
     <row r="243">
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>591.5599999999999</v>
+        <v>595.65</v>
       </c>
     </row>
     <row r="244">
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>8564.49</v>
+        <v>8623.620000000001</v>
       </c>
     </row>
     <row r="245">
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1215.8</v>
+        <v>1224.2</v>
       </c>
     </row>
     <row r="246">
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1093.94</v>
+        <v>1101.49</v>
       </c>
     </row>
     <row r="247">
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>336.13</v>
+        <v>338.45</v>
       </c>
     </row>
     <row r="248">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8118.33</v>
+        <v>8174.38</v>
       </c>
     </row>
     <row r="249">
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3228.87</v>
+        <v>3251.16</v>
       </c>
     </row>
     <row r="250">
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>26225.77</v>
+        <v>26406.83</v>
       </c>
     </row>
     <row r="251">
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1448.47</v>
+        <v>1452.95</v>
       </c>
     </row>
     <row r="252">
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2405.46</v>
+        <v>2412.89</v>
       </c>
     </row>
     <row r="253">
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>7684.76</v>
+        <v>7708.52</v>
       </c>
     </row>
     <row r="254">
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1448.19</v>
+        <v>1452.67</v>
       </c>
     </row>
     <row r="255">
@@ -16018,7 +16018,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2593.78</v>
+        <v>2601.8</v>
       </c>
     </row>
     <row r="256">
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>504.56</v>
+        <v>506.12</v>
       </c>
     </row>
     <row r="257">
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>8361.75</v>
+        <v>8387.6</v>
       </c>
     </row>
     <row r="258">
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1002.86</v>
+        <v>1005.96</v>
       </c>
     </row>
     <row r="259">
@@ -16262,7 +16262,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1434.61</v>
+        <v>1439.05</v>
       </c>
     </row>
     <row r="260">
@@ -16323,7 +16323,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>502.25</v>
+        <v>503.8</v>
       </c>
     </row>
     <row r="261">
@@ -16388,7 +16388,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>47105.53</v>
+        <v>46980.94</v>
       </c>
     </row>
     <row r="262">
@@ -16449,7 +16449,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>6776.79</v>
+        <v>6758.87</v>
       </c>
     </row>
     <row r="263">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1312.57</v>
+        <v>1309.09</v>
       </c>
     </row>
     <row r="264">
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>680.25</v>
+        <v>678.45</v>
       </c>
     </row>
     <row r="265">
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>8361.75</v>
+        <v>8339.629999999999</v>
       </c>
     </row>
     <row r="266">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>34315.41</v>
+        <v>34224.65</v>
       </c>
     </row>
     <row r="267">
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>37581.68</v>
+        <v>37482.28</v>
       </c>
     </row>
     <row r="268">
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>259.8</v>
+        <v>259.12</v>
       </c>
     </row>
     <row r="269">
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>504.56</v>
+        <v>503.23</v>
       </c>
     </row>
     <row r="270">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>469.08</v>
+        <v>462.83</v>
       </c>
     </row>
     <row r="271">
@@ -16998,7 +16998,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>469.08</v>
+        <v>462.83</v>
       </c>
     </row>
     <row r="272">
@@ -17059,7 +17059,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>450.01</v>
+        <v>444.01</v>
       </c>
     </row>
     <row r="273">
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>5196.77</v>
+        <v>5127.55</v>
       </c>
     </row>
     <row r="274">
@@ -17181,7 +17181,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>8385.52</v>
+        <v>8273.82</v>
       </c>
     </row>
     <row r="275">
@@ -17242,7 +17242,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1619.6</v>
+        <v>1598.03</v>
       </c>
     </row>
     <row r="276">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>17128.99</v>
+        <v>16900.83</v>
       </c>
     </row>
     <row r="277">
@@ -17364,7 +17364,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2114.33</v>
+        <v>2086.17</v>
       </c>
     </row>
     <row r="278">
@@ -17425,7 +17425,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>676.01</v>
+        <v>667.01</v>
       </c>
     </row>
     <row r="279">
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2809.32</v>
+        <v>2771.89</v>
       </c>
     </row>
     <row r="280">
@@ -17547,7 +17547,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>7967.21</v>
+        <v>7861.08</v>
       </c>
     </row>
     <row r="281">
@@ -17608,7 +17608,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1559.38</v>
+        <v>1538.61</v>
       </c>
     </row>
     <row r="282">
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>7967.21</v>
+        <v>7861.08</v>
       </c>
     </row>
     <row r="283">
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>530.24</v>
+        <v>523.17</v>
       </c>
     </row>
     <row r="284">
@@ -17791,7 +17791,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>229.64</v>
+        <v>226.58</v>
       </c>
     </row>
     <row r="285">
@@ -17852,7 +17852,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>5004.03</v>
+        <v>4937.37</v>
       </c>
     </row>
     <row r="286">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>7967.21</v>
+        <v>7861.08</v>
       </c>
     </row>
     <row r="287">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3788.9</v>
+        <v>3738.43</v>
       </c>
     </row>
     <row r="288">
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>503.53</v>
+        <v>493.67</v>
       </c>
     </row>
     <row r="289">
@@ -18096,7 +18096,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>612.92</v>
+        <v>600.9299999999999</v>
       </c>
     </row>
     <row r="290">
@@ -18157,7 +18157,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>8433.67</v>
+        <v>8268.59</v>
       </c>
     </row>
     <row r="291">
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>169.09</v>
+        <v>165.78</v>
       </c>
     </row>
     <row r="292">
@@ -18279,7 +18279,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>8361.75</v>
+        <v>8198.08</v>
       </c>
     </row>
     <row r="293">
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>8564.49</v>
+        <v>8396.85</v>
       </c>
     </row>
     <row r="294">
@@ -18401,7 +18401,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>666</v>
+        <v>652.97</v>
       </c>
     </row>
     <row r="295">
@@ -18462,7 +18462,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8252.620000000001</v>
       </c>
     </row>
     <row r="296">
@@ -18523,7 +18523,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1266.8</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="297">
@@ -18584,7 +18584,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>9839.049999999999</v>
+        <v>9693.280000000001</v>
       </c>
     </row>
     <row r="298">
@@ -18645,7 +18645,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>8417.379999999999</v>
+        <v>8292.66</v>
       </c>
     </row>
     <row r="299">
@@ -18706,7 +18706,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>833.8099999999999</v>
+        <v>821.46</v>
       </c>
     </row>
     <row r="300">
@@ -18767,7 +18767,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>5372.67</v>
+        <v>5293.07</v>
       </c>
     </row>
     <row r="301">
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2904.38</v>
+        <v>2861.35</v>
       </c>
     </row>
     <row r="302">
@@ -18889,7 +18889,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>8365.49</v>
+        <v>8193.57</v>
       </c>
     </row>
     <row r="303">
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>8564.49</v>
+        <v>8388.48</v>
       </c>
     </row>
     <row r="304">
@@ -19011,7 +19011,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>627.6799999999999</v>
+        <v>614.78</v>
       </c>
     </row>
     <row r="305">
@@ -19072,7 +19072,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>8365.49</v>
+        <v>8193.57</v>
       </c>
     </row>
     <row r="306">
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>11065.63</v>
+        <v>10838.21</v>
       </c>
     </row>
     <row r="307">
@@ -19194,7 +19194,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>8433.67</v>
+        <v>8260.34</v>
       </c>
     </row>
     <row r="308">
@@ -19255,7 +19255,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>23267.37</v>
+        <v>22789.18</v>
       </c>
     </row>
     <row r="309">
@@ -19316,7 +19316,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>810.8200000000001</v>
+        <v>794.16</v>
       </c>
     </row>
     <row r="310">
@@ -19377,7 +19377,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1031.08</v>
+        <v>1009.89</v>
       </c>
     </row>
     <row r="311">
@@ -19438,7 +19438,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>640.5700000000001</v>
+        <v>627.41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -15643,7 +15643,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA expressVirtual SpA</t>
+          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15247,7 +15247,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -15257,7 +15257,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17339,7 +17339,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17817,7 +17817,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18305,7 +18305,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2070,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2196,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2322,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2387,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2452,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2578,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2643,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2708,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2956,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3021,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3086,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3395,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3521,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3586,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3651,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3716,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3781,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4029,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4338,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4403,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4773,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4838,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4903,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4968,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5033,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5098,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5224,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5289,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5415,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5541,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5606,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5854,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5919,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6167,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6293,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6358,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6423,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6610,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6858,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6984,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7297,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7667,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7732,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +7858,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8045,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8232,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8297,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8606,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8732,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8858,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +8984,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9049,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9175,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9240,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9488,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9553,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9618,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9744,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9870,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +9996,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10183,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10309,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10496,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10622,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10748,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10813,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +10939,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10940,7 +11252,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11378,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11123,7 +11443,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11184,7 +11508,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11306,7 +11634,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11550,7 +11882,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11794,7 +12130,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12038,7 +12378,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12443,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12408,7 +12756,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12469,7 +12821,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12652,7 +13008,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12774,7 +13134,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12896,7 +13260,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12957,7 +13325,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13018,7 +13390,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13079,7 +13455,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13201,7 +13581,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13689,7 +14073,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13811,7 +14199,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13872,7 +14264,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14390,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14055,7 +14455,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14116,7 +14520,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14177,7 +14585,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14238,7 +14650,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14360,7 +14776,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14421,7 +14841,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14543,7 +14967,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14604,7 +15032,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14848,7 +15280,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14909,7 +15345,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15214,7 +15654,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15397,7 +15841,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15458,7 +15906,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15580,7 +16032,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15706,7 +16162,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15767,7 +16227,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15828,7 +16292,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15950,7 +16418,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16011,7 +16483,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16072,7 +16548,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16194,7 +16674,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16255,7 +16739,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16316,7 +16804,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16442,7 +16934,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16747,7 +17243,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16869,7 +17369,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17052,7 +17556,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17479,7 +17987,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17601,7 +18113,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17723,7 +18239,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17784,7 +18304,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17845,7 +18369,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17967,7 +18495,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18028,7 +18560,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18089,7 +18625,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18211,7 +18751,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18394,7 +18938,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18577,7 +19125,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19126,7 +19678,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19431,7 +19987,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M311"/>
+  <dimension ref="A1:M312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10135,7 +10135,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1078078-1632-CM26</t>
+          <t>1078078-1631-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10175,32 +10175,28 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>690.55</v>
+        <v>8641.59</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1078078-1631-CM26</t>
+          <t>1078078-1632-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10220,7 +10216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10240,22 +10236,26 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8641.59</v>
+        <v>690.55</v>
       </c>
     </row>
     <row r="157">
@@ -10326,7 +10326,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1250355-16-CM26</t>
+          <t>1078078-1621-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.933.800-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10366,22 +10366,26 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>20113.67</v>
+        <v>380.44</v>
       </c>
     </row>
     <row r="159">
@@ -10407,7 +10411,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10533,7 +10537,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10574,7 +10578,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1078078-1621-CM26</t>
+          <t>1250355-16-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10599,12 +10603,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.933.800-6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10614,26 +10618,22 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.950.108-8</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>380.44</v>
+        <v>20113.67</v>
       </c>
     </row>
     <row r="163">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1078078-1651-CM26</t>
+          <t>1078078-1652-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11435,32 +11435,28 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.437-3</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>275.85</v>
+        <v>8365.190000000001</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1078078-1649-CM26</t>
+          <t>1078078-1651-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11500,12 +11496,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11519,13 +11515,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>828.4299999999999</v>
+        <v>275.85</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1078078-1652-CM26</t>
+          <t>1078078-1649-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11545,7 +11541,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11565,28 +11561,32 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>8365.190000000001</v>
+        <v>828.4299999999999</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1078078-1647-CM26</t>
+          <t>1078078-1644-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11626,32 +11626,28 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>461.96</v>
+        <v>24056.71</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1078078-1646-CM26</t>
+          <t>1078078-1647-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11691,28 +11687,32 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7906.96</v>
+        <v>461.96</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1078078-1645-CM26</t>
+          <t>1078078-1646-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11752,12 +11752,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11767,13 +11767,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>38074.49</v>
+        <v>7906.96</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1078078-1644-CM26</t>
+          <t>1078078-1645-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>24056.71</v>
+        <v>38074.49</v>
       </c>
     </row>
     <row r="182">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -12208,7 +12208,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2291-1079-CM26</t>
+          <t>3047-297-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12233,37 +12233,41 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3512.14</v>
+        <v>6056.65</v>
       </c>
     </row>
     <row r="189">
@@ -12330,7 +12334,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3047-297-CM26</t>
+          <t>3506-436-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12350,37 +12354,37 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12389,13 +12393,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6056.65</v>
+        <v>10673.88</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3506-436-CM26</t>
+          <t>2291-1079-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12415,46 +12419,42 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>10.991.344-8</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>10673.88</v>
+        <v>3512.14</v>
       </c>
     </row>
     <row r="192">
@@ -12838,7 +12838,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1078078-1665-CM26</t>
+          <t>1078078-1671-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12893,13 +12893,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>8577.4</v>
+        <v>8107.55</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1078078-1671-CM26</t>
+          <t>1078078-1669-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12939,12 +12939,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12954,13 +12954,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>8107.55</v>
+        <v>8524.530000000001</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1078078-1670-CM26</t>
+          <t>1078078-1668-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13000,17 +13000,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13019,13 +13019,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1248.21</v>
+        <v>1085.81</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1078078-1669-CM26</t>
+          <t>1078078-1667-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -13086,7 +13086,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1078078-1668-CM26</t>
+          <t>1078078-1666-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13126,17 +13126,17 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13145,13 +13145,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1085.81</v>
+        <v>647.63</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1078078-1667-CM26</t>
+          <t>1078078-1665-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -13206,13 +13206,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>8524.530000000001</v>
+        <v>8577.4</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1078078-1666-CM26</t>
+          <t>1078078-1664-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13252,17 +13252,17 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13271,13 +13271,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>647.63</v>
+        <v>1299.84</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1078078-1664-CM26</t>
+          <t>1078078-1670-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -13317,17 +13317,17 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13336,13 +13336,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1299.84</v>
+        <v>1248.21</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2322-382-CM26</t>
+          <t>1078078-1662-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13367,27 +13367,27 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -13401,13 +13401,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4700.4</v>
+        <v>815.75</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1078078-1662-CM26</t>
+          <t>1078078-1663-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13447,32 +13447,28 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>815.75</v>
+        <v>8520.719999999999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1078078-1661-CM26</t>
+          <t>1346281-88-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13492,32 +13488,32 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13527,13 +13523,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>9254.27</v>
+        <v>1035.81</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1078078-1660-CM26</t>
+          <t>1078078-1658-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13553,7 +13549,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -13573,32 +13569,28 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.437-3</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>884.76</v>
+        <v>9254.27</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1078078-1659-CM26</t>
+          <t>2322-382-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13618,48 +13610,52 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>9254.27</v>
+        <v>4700.4</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1078078-1658-CM26</t>
+          <t>1078078-1660-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13679,7 +13675,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -13699,28 +13695,32 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>9254.27</v>
+        <v>884.76</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1346281-88-CM26</t>
+          <t>1078078-1661-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13745,27 +13745,27 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13775,13 +13775,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1035.81</v>
+        <v>9254.27</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1078078-1663-CM26</t>
+          <t>1078078-1659-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13836,7 +13836,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>8520.719999999999</v>
+        <v>9254.27</v>
       </c>
     </row>
     <row r="214">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -14281,7 +14281,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1078078-1677-CM26</t>
+          <t>1078078-1678-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -14321,28 +14321,32 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>8554.16</v>
+        <v>576.01</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1078078-1678-CM26</t>
+          <t>1078078-1677-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14362,7 +14366,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -14382,32 +14386,28 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>576.01</v>
+        <v>8554.16</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1078078-1675-CM26</t>
+          <t>1078078-1673-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -14466,13 +14466,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>267.99</v>
+        <v>1134.53</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1078078-1674-CM26</t>
+          <t>1078078-1672-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -14531,13 +14531,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>254.61</v>
+        <v>918.38</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1078078-1673-CM26</t>
+          <t>898-2056-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14557,52 +14557,48 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1134.53</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1078078-1672-CM26</t>
+          <t>527481-61-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14627,32 +14623,32 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14661,13 +14657,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>918.38</v>
+        <v>14144.49</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>898-2056-CM26</t>
+          <t>4968-867-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14692,12 +14688,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14707,28 +14703,32 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>271.2</v>
+        <v>1307.11</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>527481-61-CM26</t>
+          <t>1078078-1675-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14748,37 +14748,37 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14787,13 +14787,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>14144.49</v>
+        <v>267.99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4968-867-CM26</t>
+          <t>1078078-1674-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14818,32 +14818,32 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -14852,13 +14852,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1307.11</v>
+        <v>254.61</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1078078-1676-CM26</t>
+          <t>1078078-1697-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -14898,28 +14898,32 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>9043.969999999999</v>
+        <v>175.22</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3596-479-CM26</t>
+          <t>1078078-1695-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14939,32 +14943,32 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -14978,13 +14982,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3194.81</v>
+        <v>155.07</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1078078-1695-CM26</t>
+          <t>1078078-1696-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15024,32 +15028,28 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>155.07</v>
+        <v>8419.48</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1078078-1696-CM26</t>
+          <t>1078078-1687-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15089,28 +15089,32 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>8419.48</v>
+        <v>1224.2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1078078-1701-CM26</t>
+          <t>1078078-1699-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15130,7 +15134,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -15171,7 +15175,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1078078-1699-CM26</t>
+          <t>1078078-1700-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15191,7 +15195,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -15211,28 +15215,32 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>17811.13</v>
+        <v>279.49</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1078078-1700-CM26</t>
+          <t>1078078-1701-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15272,32 +15280,28 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.897.437-3</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>279.49</v>
+        <v>17811.13</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1078078-1694-CM26</t>
+          <t>3596-479-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15317,32 +15321,32 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -15356,7 +15360,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>371.79</v>
+        <v>3194.81</v>
       </c>
     </row>
     <row r="238">
@@ -15382,7 +15386,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -15423,7 +15427,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1078078-1693-CM26</t>
+          <t>1078078-1694-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15463,28 +15467,32 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>8011.22</v>
+        <v>371.79</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1078078-1686-CM26</t>
+          <t>2069-5561-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15509,12 +15517,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15524,28 +15532,32 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr"/>
+          <t>77.765.995-2</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8822.469999999999</v>
+        <v>8174.38</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1078078-1691-CM26</t>
+          <t>1078078-1692-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15565,7 +15577,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -15585,28 +15597,32 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>8822.469999999999</v>
+        <v>1101.49</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1078078-1690-CM26</t>
+          <t>1078078-1691-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15626,7 +15642,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -15646,32 +15662,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3118.84</v>
+        <v>8822.469999999999</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1078078-1689-CM26</t>
+          <t>1078078-1690-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15711,28 +15723,32 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>595.65</v>
+        <v>3118.84</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1078078-1688-CM26</t>
+          <t>1078078-1689-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15787,13 +15803,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>8623.620000000001</v>
+        <v>595.65</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1078078-1687-CM26</t>
+          <t>1078078-1688-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15813,7 +15829,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15833,32 +15849,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1224.2</v>
+        <v>8623.620000000001</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1078078-1692-CM26</t>
+          <t>1078078-1686-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15898,26 +15910,22 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1101.49</v>
+        <v>8822.469999999999</v>
       </c>
     </row>
     <row r="247">
@@ -15943,7 +15951,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -15984,7 +15992,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2069-5561-CM26</t>
+          <t>1078078-1693-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16009,12 +16017,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16024,26 +16032,22 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8174.38</v>
+        <v>8011.22</v>
       </c>
     </row>
     <row r="249">
@@ -16179,7 +16183,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2788-578-CM26</t>
+          <t>2412-385-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16204,12 +16208,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16238,7 +16242,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1452.95</v>
+        <v>2601.8</v>
       </c>
     </row>
     <row r="252">
@@ -16329,7 +16333,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -16390,7 +16394,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -16435,7 +16439,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2412-385-CM26</t>
+          <t>2788-578-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16460,12 +16464,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16494,7 +16498,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2601.8</v>
+        <v>1452.95</v>
       </c>
     </row>
     <row r="256">
@@ -16520,7 +16524,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -16711,7 +16715,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -16906,7 +16910,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -16951,7 +16955,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5349-1254-CM26</t>
+          <t>1078078-1712-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16971,48 +16975,52 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1309.09</v>
+        <v>552.59</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1078078-1710-CM26</t>
+          <t>5349-1254-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17037,27 +17045,27 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -17067,7 +17075,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>678.45</v>
+        <v>1309.09</v>
       </c>
     </row>
     <row r="265">
@@ -17134,7 +17142,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3477-446-CM26</t>
+          <t>1078078-1708-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17154,48 +17162,52 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>34224.65</v>
+        <v>503.23</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2674-545-CM26</t>
+          <t>3477-446-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17220,47 +17232,43 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>37482.28</v>
+        <v>34224.65</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1057461-870-CM26</t>
+          <t>2674-545-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17285,43 +17293,47 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>259.12</v>
+        <v>37482.28</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1078078-1708-CM26</t>
+          <t>1057461-870-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17346,47 +17358,43 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>503.23</v>
+        <v>259.12</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1078078-1723-CM26</t>
+          <t>1078078-1710-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17401,12 +17409,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -17426,12 +17434,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -17441,13 +17449,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>462.83</v>
+        <v>678.45</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1078078-1729-CM26</t>
+          <t>1078078-1723-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17467,7 +17475,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -17508,7 +17516,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1078078-1728-CM26</t>
+          <t>1078078-1729-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17548,32 +17556,28 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>444.01</v>
+        <v>462.83</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1078078-1727-CM26</t>
+          <t>1078078-1728-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17613,28 +17617,32 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr"/>
+          <t>77.721.492-6</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>5127.55</v>
+        <v>444.01</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1078078-1726-CM26</t>
+          <t>1078078-1730-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17674,12 +17682,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17689,13 +17697,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>8273.82</v>
+        <v>2086.17</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1078078-1725-CM26</t>
+          <t>1078078-1727-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17735,12 +17743,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17750,13 +17758,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1598.03</v>
+        <v>5127.55</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1078078-1724-CM26</t>
+          <t>1078078-1726-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17811,13 +17819,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>16900.83</v>
+        <v>8273.82</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1078078-1730-CM26</t>
+          <t>1078078-1725-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17837,7 +17845,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -17857,12 +17865,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17872,13 +17880,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2086.17</v>
+        <v>1598.03</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1078078-1722-CM26</t>
+          <t>1078078-1724-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17918,12 +17926,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -17933,13 +17941,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>667.01</v>
+        <v>16900.83</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1078078-1720-CM26</t>
+          <t>1078078-1722-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17979,32 +17987,28 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2771.89</v>
+        <v>667.01</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1078078-1721-CM26</t>
+          <t>1078078-1716-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18044,28 +18048,32 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>7861.08</v>
+        <v>226.58</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1078078-1719-CM26</t>
+          <t>1078078-1721-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18085,7 +18093,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -18105,32 +18113,28 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1538.61</v>
+        <v>7861.08</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1078078-1718-CM26</t>
+          <t>1078078-1720-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18170,28 +18174,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>7861.08</v>
+        <v>2771.89</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1078078-1717-CM26</t>
+          <t>1078078-1719-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18211,7 +18219,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -18250,13 +18258,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>523.17</v>
+        <v>1538.61</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1078078-1716-CM26</t>
+          <t>1078078-1718-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18276,7 +18284,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -18296,32 +18304,28 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>226.58</v>
+        <v>7861.08</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1078078-1715-CM26</t>
+          <t>1078078-1717-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18380,13 +18384,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4937.37</v>
+        <v>523.17</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1078078-1709-CM26</t>
+          <t>1078078-1715-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18426,28 +18430,32 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>7861.08</v>
+        <v>4937.37</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>758-456-CM26</t>
+          <t>1078078-1709-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18472,7 +18480,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -18487,32 +18495,28 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3738.43</v>
+        <v>7861.08</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1078078-1741-CM26</t>
+          <t>758-456-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18527,17 +18531,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -18571,13 +18575,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>493.67</v>
+        <v>3738.43</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1078078-1739-CM26</t>
+          <t>1078078-1741-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18617,12 +18621,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -18636,13 +18640,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>600.9299999999999</v>
+        <v>493.67</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1078078-1738-CM26</t>
+          <t>1078078-1740-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18697,13 +18701,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>8268.59</v>
+        <v>8198.08</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1078078-1737-CM26</t>
+          <t>1078078-1739-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18723,7 +18727,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -18743,17 +18747,17 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -18762,13 +18766,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>165.78</v>
+        <v>600.9299999999999</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1078078-1740-CM26</t>
+          <t>1078078-1738-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18823,13 +18827,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>8198.08</v>
+        <v>8268.59</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1078078-1735-CM26</t>
+          <t>1078078-1737-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18869,28 +18873,32 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr"/>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>8396.85</v>
+        <v>165.78</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1078078-1734-CM26</t>
+          <t>1078078-1735-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18930,32 +18938,28 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>652.97</v>
+        <v>8396.85</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1078078-1733-CM26</t>
+          <t>1078078-1734-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18995,28 +18999,32 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>8252.620000000001</v>
+        <v>652.97</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1078078-1736-CM26</t>
+          <t>1078078-1733-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19056,12 +19064,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -19071,13 +19079,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1242</v>
+        <v>8252.620000000001</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1057486-326-CM26</t>
+          <t>1078078-1736-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19092,7 +19100,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -19102,12 +19110,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.608.400-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19117,32 +19125,28 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>9693.280000000001</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1078078-1731-CM26</t>
+          <t>1057486-326-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19167,12 +19171,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.608.400-3</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19182,28 +19186,32 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>8292.66</v>
+        <v>9693.280000000001</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1078078-1732-CM26</t>
+          <t>1078078-1731-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19243,12 +19251,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19258,13 +19266,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>821.46</v>
+        <v>8292.66</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4494-423-CM26</t>
+          <t>1078078-1732-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19284,32 +19292,32 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -19319,13 +19327,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>5293.07</v>
+        <v>821.46</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2676-389-CM26</t>
+          <t>4494-423-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19350,27 +19358,27 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -19380,13 +19388,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2861.35</v>
+        <v>5293.07</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1078078-1748-CM26</t>
+          <t>2676-389-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19401,7 +19409,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -19411,12 +19419,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19426,12 +19434,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -19441,13 +19449,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>8193.57</v>
+        <v>2861.35</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1078078-1747-CM26</t>
+          <t>1078078-1745-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19502,13 +19510,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>8388.48</v>
+        <v>614.78</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1078078-1745-CM26</t>
+          <t>1078078-1748-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19563,13 +19571,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>614.78</v>
+        <v>8193.57</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1078078-1744-CM26</t>
+          <t>1078078-1747-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19624,13 +19632,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>8193.57</v>
+        <v>8388.48</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2273-381-CM26</t>
+          <t>1078078-1744-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19650,17 +19658,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19670,32 +19678,28 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>10838.21</v>
+        <v>8193.57</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1078078-1742-CM26</t>
+          <t>1078078-1749-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19715,7 +19719,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -19735,12 +19739,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19750,13 +19754,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>8260.34</v>
+        <v>794.16</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>3340-175-CM26</t>
+          <t>1078078-1742-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19781,27 +19785,27 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19811,13 +19815,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>22789.18</v>
+        <v>8260.34</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1078078-1749-CM26</t>
+          <t>3340-175-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19842,27 +19846,27 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -19872,13 +19876,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>794.16</v>
+        <v>22789.18</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1078078-1743-CM26</t>
+          <t>2273-381-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19903,12 +19907,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19918,86 +19922,151 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr"/>
+          <t>77.801.815-2</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1009.89</v>
+        <v>10838.21</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
+          <t>1078078-1743-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>60.509.001-K</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>ABATTE OFFICITY</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>96.909.950-0</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>1009.89</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
           <t>1078078-1750-CM26</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>60.509.001-K</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
         <is>
           <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
-      <c r="J311" t="inlineStr">
+      <c r="J312" t="inlineStr">
         <is>
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M311" s="2" t="n">
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
         <v>627.41</v>
       </c>
     </row>
